--- a/artfynd/A 37033-2025 artfynd.xlsx
+++ b/artfynd/A 37033-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2444,6 +2444,983 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129296227</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92864</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Barrskog vid Kvarngölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>535953</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6415679</v>
+      </c>
+      <c r="S18" t="n">
+        <v>8</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>William Rosén, Ida Bronner Thelin, Jens Annamatz Ranvide</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129296503</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92826</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Barrskog vid Kvarngölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>535968</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6415881</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>William Rosén, Ida Bronner Thelin, Jens Annamatz Ranvide</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129296321</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79658</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Barrskog vid Kvarngölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>535889</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6415733</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>William Rosén, Ida Bronner Thelin, Jens Annamatz Ranvide</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129296202</v>
+      </c>
+      <c r="B21" t="n">
+        <v>95994</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Barrskog vid Kvarngölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>535929</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6415681</v>
+      </c>
+      <c r="S21" t="n">
+        <v>8</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>William Rosén, Ida Bronner Thelin, Jens Annamatz Ranvide</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129296189</v>
+      </c>
+      <c r="B22" t="n">
+        <v>95983</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Barrskog vid Kvarngölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>535929</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6415681</v>
+      </c>
+      <c r="S22" t="n">
+        <v>8</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>William Rosén, Ida Bronner Thelin, Jens Annamatz Ranvide</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129296340</v>
+      </c>
+      <c r="B23" t="n">
+        <v>96265</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Barrskog vid Kvarngölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>535889</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6415733</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>William Rosén, Ida Bronner Thelin, Jens Annamatz Ranvide</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129296351</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92826</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Barrskog vid Kvarngölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>535889</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6415733</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>William Rosén, Ida Bronner Thelin, Jens Annamatz Ranvide</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129296476</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91940</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Barrskog vid Kvarngölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>535988</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6415914</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Stump # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>William Rosén, Ida Bronner Thelin, Jens Annamatz Ranvide</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37033-2025 artfynd.xlsx
+++ b/artfynd/A 37033-2025 artfynd.xlsx
@@ -2449,7 +2449,7 @@
         <v>129296227</v>
       </c>
       <c r="B18" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>129296503</v>
       </c>
       <c r="B19" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>129296202</v>
       </c>
       <c r="B21" t="n">
-        <v>95994</v>
+        <v>96001</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>129296189</v>
       </c>
       <c r="B22" t="n">
-        <v>95983</v>
+        <v>95990</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>129296340</v>
       </c>
       <c r="B23" t="n">
-        <v>96265</v>
+        <v>96272</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>129296351</v>
       </c>
       <c r="B24" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>129296476</v>
       </c>
       <c r="B25" t="n">
-        <v>91940</v>
+        <v>91947</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 37033-2025 artfynd.xlsx
+++ b/artfynd/A 37033-2025 artfynd.xlsx
@@ -2449,7 +2449,7 @@
         <v>129296227</v>
       </c>
       <c r="B18" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>129296503</v>
       </c>
       <c r="B19" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>129296321</v>
       </c>
       <c r="B20" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>129296202</v>
       </c>
       <c r="B21" t="n">
-        <v>96001</v>
+        <v>96003</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>129296189</v>
       </c>
       <c r="B22" t="n">
-        <v>95990</v>
+        <v>95992</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>129296340</v>
       </c>
       <c r="B23" t="n">
-        <v>96272</v>
+        <v>96274</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>129296351</v>
       </c>
       <c r="B24" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>129296476</v>
       </c>
       <c r="B25" t="n">
-        <v>91947</v>
+        <v>91949</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 37033-2025 artfynd.xlsx
+++ b/artfynd/A 37033-2025 artfynd.xlsx
@@ -2921,7 +2921,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>William Rosén, Ida Bronner Thelin, Jens Annamatz Ranvide</t>
+          <t>Jens Annamatz Ranvide, Ida Bronner Thelin, William Rosén</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>William Rosén, Ida Bronner Thelin, Jens Annamatz Ranvide</t>
+          <t>Jens Annamatz Ranvide, Ida Bronner Thelin, William Rosén</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 37033-2025 artfynd.xlsx
+++ b/artfynd/A 37033-2025 artfynd.xlsx
@@ -2449,7 +2449,7 @@
         <v>129296227</v>
       </c>
       <c r="B18" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>129296503</v>
       </c>
       <c r="B19" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>129296202</v>
       </c>
       <c r="B21" t="n">
-        <v>96003</v>
+        <v>96029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jens Annamatz Ranvide, Ida Bronner Thelin, William Rosén</t>
+          <t>William Rosén, Ida Bronner Thelin, Jens Annamatz Ranvide</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2931,7 +2931,7 @@
         <v>129296189</v>
       </c>
       <c r="B22" t="n">
-        <v>95992</v>
+        <v>96018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jens Annamatz Ranvide, Ida Bronner Thelin, William Rosén</t>
+          <t>William Rosén, Ida Bronner Thelin, Jens Annamatz Ranvide</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3048,7 +3048,7 @@
         <v>129296340</v>
       </c>
       <c r="B23" t="n">
-        <v>96274</v>
+        <v>96300</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>129296351</v>
       </c>
       <c r="B24" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>129296476</v>
       </c>
       <c r="B25" t="n">
-        <v>91949</v>
+        <v>91957</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 37033-2025 artfynd.xlsx
+++ b/artfynd/A 37033-2025 artfynd.xlsx
@@ -2449,7 +2449,7 @@
         <v>129296227</v>
       </c>
       <c r="B18" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>129296503</v>
       </c>
       <c r="B19" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>129296202</v>
       </c>
       <c r="B21" t="n">
-        <v>96029</v>
+        <v>96030</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>129296189</v>
       </c>
       <c r="B22" t="n">
-        <v>96018</v>
+        <v>96019</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>129296340</v>
       </c>
       <c r="B23" t="n">
-        <v>96300</v>
+        <v>96301</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>129296351</v>
       </c>
       <c r="B24" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>129296476</v>
       </c>
       <c r="B25" t="n">
-        <v>91957</v>
+        <v>91958</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 37033-2025 artfynd.xlsx
+++ b/artfynd/A 37033-2025 artfynd.xlsx
@@ -2799,7 +2799,7 @@
         <v>129296202</v>
       </c>
       <c r="B21" t="n">
-        <v>96030</v>
+        <v>96031</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>129296189</v>
       </c>
       <c r="B22" t="n">
-        <v>96019</v>
+        <v>96020</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>129296340</v>
       </c>
       <c r="B23" t="n">
-        <v>96301</v>
+        <v>96302</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 37033-2025 artfynd.xlsx
+++ b/artfynd/A 37033-2025 artfynd.xlsx
@@ -2449,7 +2449,7 @@
         <v>129296227</v>
       </c>
       <c r="B18" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>129296503</v>
       </c>
       <c r="B19" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>129296321</v>
       </c>
       <c r="B20" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>129296202</v>
       </c>
       <c r="B21" t="n">
-        <v>96031</v>
+        <v>96035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>129296189</v>
       </c>
       <c r="B22" t="n">
-        <v>96020</v>
+        <v>96024</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>129296340</v>
       </c>
       <c r="B23" t="n">
-        <v>96302</v>
+        <v>96306</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>129296351</v>
       </c>
       <c r="B24" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>129296476</v>
       </c>
       <c r="B25" t="n">
-        <v>91958</v>
+        <v>91961</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 37033-2025 artfynd.xlsx
+++ b/artfynd/A 37033-2025 artfynd.xlsx
@@ -2449,7 +2449,7 @@
         <v>129296227</v>
       </c>
       <c r="B18" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>129296503</v>
       </c>
       <c r="B19" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>129296321</v>
       </c>
       <c r="B20" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>129296202</v>
       </c>
       <c r="B21" t="n">
-        <v>96081</v>
+        <v>96093</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>129296189</v>
       </c>
       <c r="B22" t="n">
-        <v>96070</v>
+        <v>96082</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>129296340</v>
       </c>
       <c r="B23" t="n">
-        <v>96352</v>
+        <v>96364</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>129296351</v>
       </c>
       <c r="B24" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>129296476</v>
       </c>
       <c r="B25" t="n">
-        <v>91999</v>
+        <v>92005</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 37033-2025 artfynd.xlsx
+++ b/artfynd/A 37033-2025 artfynd.xlsx
@@ -2449,7 +2449,7 @@
         <v>129296227</v>
       </c>
       <c r="B18" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>129296503</v>
       </c>
       <c r="B19" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>129296321</v>
       </c>
       <c r="B20" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>129296202</v>
       </c>
       <c r="B21" t="n">
-        <v>96093</v>
+        <v>96094</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>129296189</v>
       </c>
       <c r="B22" t="n">
-        <v>96082</v>
+        <v>96083</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>129296340</v>
       </c>
       <c r="B23" t="n">
-        <v>96364</v>
+        <v>96365</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>129296351</v>
       </c>
       <c r="B24" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>129296476</v>
       </c>
       <c r="B25" t="n">
-        <v>92005</v>
+        <v>92006</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
